--- a/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
@@ -639,13 +639,13 @@
         <v>8.109999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -662,22 +662,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -904,22 +907,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>51.52</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>51.52</v>
       </c>
     </row>
   </sheetData>
@@ -1541,13 +1547,13 @@
         <v>8.109999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>8.109999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1564,22 +1570,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1806,22 +1815,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>51.52</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>51.52</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
@@ -662,25 +662,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -732,25 +732,25 @@
         <v>22</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>27.27</v>
+        <v>18.18</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -767,25 +767,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>51.52</v>
+        <v>69.7</v>
       </c>
       <c r="H9" s="1">
-        <v>48.48</v>
+        <v>30.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>48.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -907,25 +907,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>48.48</v>
+        <v>69.7</v>
       </c>
       <c r="H13" s="1">
-        <v>51.52</v>
+        <v>30.3</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="J13">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>51.52</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1250,22 +1250,25 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>13.51</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1282,22 +1285,25 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>73.17</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>26.83</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.9</v>
       </c>
       <c r="J11">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1314,22 +1320,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>94.44</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>5.56</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.6</v>
       </c>
       <c r="J12">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1346,22 +1355,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.1</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>21.21</v>
       </c>
     </row>
   </sheetData>
@@ -1570,25 +1582,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1640,25 +1652,25 @@
         <v>22</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>27.27</v>
+        <v>18.18</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1675,25 +1687,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>51.52</v>
+        <v>69.7</v>
       </c>
       <c r="H9" s="1">
-        <v>48.48</v>
+        <v>30.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.3</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>48.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1710,16 +1722,16 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>91.89</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>8.109999999999999</v>
+        <v>13.51</v>
       </c>
       <c r="I10" s="2">
         <v>8.5</v>
@@ -1745,19 +1757,19 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>82.93000000000001</v>
+        <v>73.17</v>
       </c>
       <c r="H11" s="1">
-        <v>17.07</v>
+        <v>26.83</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1792,7 +1804,7 @@
         <v>5.56</v>
       </c>
       <c r="I12" s="2">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1815,25 +1827,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>48.48</v>
+        <v>69.7</v>
       </c>
       <c r="H13" s="1">
-        <v>51.52</v>
+        <v>30.3</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J13">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>51.52</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
@@ -534,13 +534,13 @@
         <v>26.83</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -569,13 +569,13 @@
         <v>25.71</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -604,13 +604,13 @@
         <v>31.43</v>
       </c>
       <c r="I4" s="2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -994,22 +994,25 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>19.51</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1026,22 +1029,25 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1058,22 +1064,25 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.5</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1090,22 +1099,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>91.89</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1122,22 +1134,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>97.22</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>2.78</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1154,22 +1169,25 @@
         <v>22</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.5</v>
       </c>
       <c r="J7">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1186,22 +1204,25 @@
         <v>22</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>59.09</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>40.91</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.4</v>
       </c>
       <c r="J8">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1218,22 +1239,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>45.45</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>54.55</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1442,25 +1466,25 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>73.17</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>26.83</v>
+        <v>19.51</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1477,25 +1501,25 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>74.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>25.71</v>
+        <v>14.29</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1512,25 +1536,25 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
-        <v>68.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>31.43</v>
+        <v>14.29</v>
       </c>
       <c r="I4" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1559,7 +1583,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1582,19 +1606,19 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>97.22</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1629,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1664,7 +1688,7 @@
         <v>18.18</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1687,19 +1711,19 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>69.7</v>
+        <v>66.67</v>
       </c>
       <c r="H9" s="1">
-        <v>30.3</v>
+        <v>33.33</v>
       </c>
       <c r="I9" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
@@ -1111,13 +1111,13 @@
         <v>8.109999999999999</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1571,19 +1571,19 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>91.89</v>
+        <v>94.59</v>
       </c>
       <c r="H5" s="1">
-        <v>8.109999999999999</v>
+        <v>5.41</v>
       </c>
       <c r="I5" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1618,7 +1618,7 @@
         <v>2.78</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1746,19 +1746,19 @@
         <v>37</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>86.48999999999999</v>
+        <v>94.59</v>
       </c>
       <c r="H10" s="1">
-        <v>13.51</v>
+        <v>5.41</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1781,19 +1781,19 @@
         <v>41</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1">
-        <v>73.17</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>26.83</v>
+        <v>19.51</v>
       </c>
       <c r="I11" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1816,19 +1816,19 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="H12" s="1">
-        <v>5.56</v>
+        <v>2.78</v>
       </c>
       <c r="I12" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20212.xlsx
@@ -534,13 +534,13 @@
         <v>26.83</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1006,13 +1006,13 @@
         <v>19.51</v>
       </c>
       <c r="I2" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1204,25 +1204,25 @@
         <v>22</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>59.09</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>40.91</v>
+        <v>18.18</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1239,25 +1239,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>45.45</v>
+        <v>69.7</v>
       </c>
       <c r="H9" s="1">
-        <v>54.55</v>
+        <v>30.3</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1379,25 +1379,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>66.67</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>33.33</v>
+        <v>15.15</v>
       </c>
       <c r="I13" s="2">
         <v>7.1</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1466,25 +1466,25 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>80.48999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="H2" s="1">
-        <v>19.51</v>
+        <v>12.2</v>
       </c>
       <c r="I2" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1501,19 +1501,19 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1536,19 +1536,19 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1676,19 +1676,19 @@
         <v>22</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>81.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1711,19 +1711,19 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>66.67</v>
+        <v>90.91</v>
       </c>
       <c r="H9" s="1">
-        <v>33.33</v>
+        <v>9.09</v>
       </c>
       <c r="I9" s="2">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1851,19 +1851,19 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>69.7</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>30.3</v>
+        <v>18.18</v>
       </c>
       <c r="I13" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J13">
         <v>0</v>
